--- a/_authoring/science_2026-27/_toolchain/scheme_references/GROW_SOW.xlsx
+++ b/_authoring/science_2026-27/_toolchain/scheme_references/GROW_SOW.xlsx
@@ -8142,7 +8142,7 @@
     <row r="65" ht="19.5" customHeight="1" s="66">
       <c r="A65" s="80" t="inlineStr">
         <is>
-          <t>SUMMER TERM 2  ·  June, end of academic year 2027</t>
+          <t>SUMMER TERM 2  ·  21 July, end of academic year 2027</t>
         </is>
       </c>
       <c r="B65" s="84" t="n"/>
